--- a/BSI.IT.27.C7/BSI.IT.27.C7_E09_Sample of 1 MIA25142 Workpaper.xlsx
+++ b/BSI.IT.27.C7/BSI.IT.27.C7_E09_Sample of 1 MIA25142 Workpaper.xlsx
@@ -1107,7 +1107,7 @@
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>E04; E05; E06 tab 2_Step-by-Step 4.1</t>
+          <t>E04 tab 2_Cisco Network Administrators; E05 tab 2.Cisco Network Administrators; E06 tab 2_Step-by-Step 4.1</t>
         </is>
       </c>
       <c r="E5" s="32" t="inlineStr">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>E04 (tab 2); E02 4.1.1 C1, sec. 8 steps 1-7</t>
+          <t>E04 (tab 2_Cisco Network Administrators); E02 4.1.1 C1, sec. 8 steps 1-7</t>
         </is>
       </c>
       <c r="E6" s="32" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>E04 (rows 2538-2539; AD extract row 1639); E03 sec. 3.3</t>
+          <t>E04 (tab 2_Cisco Network Administrators, rows 2538-2539; tabs 2_Cisco Network Administrators and 3_ISEAdmin, AD extract 11/25/2025, row 1639); E03 sec. 3.3</t>
         </is>
       </c>
       <c r="E7" s="32" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>E04 (rows 2538-2539); E02 4.1.1 C2; E01 SUS.IAMS.4.2.5.6</t>
+          <t>E04 (tab 2_Cisco Network Administrators, rows 2538-2539); E02 4.1.1 C2; E01 SUS.IAMS.4.2.5.6</t>
         </is>
       </c>
       <c r="E8" s="32" t="inlineStr">
@@ -1255,7 +1255,7 @@
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>E04 (rows 2538-2539); E02 sec. 8 step 8</t>
+          <t>E04 (tab 2_Cisco Network Administrators, rows 2538-2539); E02 sec. 8 step 8</t>
         </is>
       </c>
       <c r="E9" s="32" t="inlineStr">
@@ -1292,7 +1292,7 @@
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>E04 (rows 2538-2539); E01 SUS.IAMS.4.2.5.1, 4.2.5.7</t>
+          <t>E04 (tab 2_Cisco Network Administrators, rows 2538-2539); E01 SUS.IAMS.4.2.5.1, 4.2.5.7</t>
         </is>
       </c>
       <c r="E10" s="32" t="inlineStr">
@@ -1329,7 +1329,7 @@
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>E04 Netwrix log; E02 4.1.1 C3-C4, step 10; E01 SUS.IAMS.4.2.5.10</t>
+          <t>E04 tabs 2_Cisco Network Administrators and 3_ISEAdmin, section REVOCATION EVIDENCE, row 2976 (Netwrix log); E02 4.1.1 C3-C4, step 10; E01 SUS.IAMS.4.2.5.10</t>
         </is>
       </c>
       <c r="E11" s="32" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>E04; E01 SUS.IAMS.4.2.5.21</t>
+          <t>E04 tabs 2_Cisco Network Administrators and 3_ISEAdmin, section REVOCATION EVIDENCE, row 2976 (Netwrix log); E01 SUS.IAMS.4.2.5.21</t>
         </is>
       </c>
       <c r="E12" s="32" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>E04 AD row 1639; E06 4_Item Detail rows 19, 57; E06 5_Exceptions row 8</t>
+          <t>E04 tabs 2_Cisco Network Administrators and 3_ISEAdmin, AD extract 11/25/2025, row 1639; E06 4_Item Detail rows 19, 57; E06 5_Exceptions row 8</t>
         </is>
       </c>
       <c r="E13" s="29" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>E05 rows 3260, 3265; E06 4_Item Detail rows 107, 130</t>
+          <t>E05 tab 2.Cisco Network Administrators, rows 3260, 3265; E06 4_Item Detail rows 107, 130</t>
         </is>
       </c>
       <c r="E14" s="29" t="inlineStr">
@@ -1669,12 +1669,12 @@
       </c>
       <c r="C5" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx; E05 BSI.IT.27.C7.02 Q1 2026 Cert.xlsx</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx; E05 BSI.IT.27.C7_E05_Q1 2026 Cert.xlsx</t>
         </is>
       </c>
       <c r="D5" s="24" t="inlineStr">
         <is>
-          <t>Certification Name / launch dates (8/1/2025; 4/9/2026)</t>
+          <t>E04 tab 2_Cisco Network Administrators / E05 tab 2.Cisco Network Administrators – Certification Name / launch dates (8/1/2025; 4/9/2026)</t>
         </is>
       </c>
       <c r="E5" s="24" t="inlineStr">
@@ -1696,12 +1696,12 @@
       </c>
       <c r="C6" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx</t>
         </is>
       </c>
       <c r="D6" s="24" t="inlineStr">
         <is>
-          <t>Tab 2 – Certification Name "2025 Q3 PAM BSI SOX Manager Certification"</t>
+          <t>Tab 2_Cisco Network Administrators – Certification Name "2025 Q3 PAM BSI SOX Manager Certification"</t>
         </is>
       </c>
       <c r="E6" s="24" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="C7" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx; E03 Definition of Privilege</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx; E03 Definition of Privilege</t>
         </is>
       </c>
       <c r="D7" s="24" t="inlineStr">
         <is>
-          <t>Rows 2538-2539 (Entitlement Value); AD extract row 1639; sec. 3.3</t>
+          <t>tab 2_Cisco Network Administrators, rows 2538-2539 (Entitlement Value); tabs 2_Cisco Network Administrators and 3_ISEAdmin, AD extract 11/25/2025, row 1639; sec. 3.3</t>
         </is>
       </c>
       <c r="E7" s="24" t="inlineStr">
@@ -1750,12 +1750,12 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
         <is>
-          <t>Rows 2538-2539 – Manager Name, Decision Maker</t>
+          <t>tab 2_Cisco Network Administrators, rows 2538-2539 – Manager Name, Decision Maker</t>
         </is>
       </c>
       <c r="E8" s="24" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
         <is>
-          <t>Rows 2538-2539 – Decision, Decision Date, SignOff Date</t>
+          <t>tab 2_Cisco Network Administrators, rows 2538-2539 – Decision, Decision Date, SignOff Date</t>
         </is>
       </c>
       <c r="E9" s="24" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="C10" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx</t>
         </is>
       </c>
       <c r="D10" s="24" t="inlineStr">
         <is>
-          <t>Rows 2538-2539 – Decision = Revoked</t>
+          <t>tab 2_Cisco Network Administrators, rows 2538-2539 – Decision = Revoked</t>
         </is>
       </c>
       <c r="E10" s="24" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="C11" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx (Netwrix tab)</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx</t>
         </is>
       </c>
       <c r="D11" s="24" t="inlineStr">
         <is>
-          <t>Netwrix "member removed" events 09/02/2025 – CISCO Network Administrators, ISEAdmin</t>
+          <t>tabs 2_Cisco Network Administrators and 3_ISEAdmin, section REVOCATION EVIDENCE, row 2976 (Netwrix log) – "member removed" 09/02/2025, CISCO Network Administrators and ISEAdmin</t>
         </is>
       </c>
       <c r="E11" s="24" t="inlineStr">
@@ -1858,12 +1858,12 @@
       </c>
       <c r="C12" s="24" t="inlineStr">
         <is>
-          <t>E04 Netwrix log; E01 IAM Standard</t>
+          <t>E04 tabs 2_Cisco Network Administrators and 3_ISEAdmin, section REVOCATION EVIDENCE, row 2976 (Netwrix log); E01 IAM Standard</t>
         </is>
       </c>
       <c r="D12" s="24" t="inlineStr">
         <is>
-          <t>Removal 09/02/2025 vs deadline 10/10/2025; SUS.IAMS.4.2.5.21 (p.22)</t>
+          <t>tabs 2_Cisco Network Administrators and 3_ISEAdmin, section REVOCATION EVIDENCE, row 2976 (Netwrix log): removal 09/02/2025 vs deadline 10/10/2025; SUS.IAMS.4.2.5.21 (p.22)</t>
         </is>
       </c>
       <c r="E12" s="24" t="inlineStr">
@@ -1885,12 +1885,12 @@
       </c>
       <c r="C13" s="24" t="inlineStr">
         <is>
-          <t>E04 BSI.IT.27.C7.02 Q3_2025.xlsx (AD extract); E06 walkthrough</t>
+          <t>E04 BSI.IT.27.C7_E04_Q3_2025.xlsx; E06 walkthrough</t>
         </is>
       </c>
       <c r="D13" s="24" t="inlineStr">
         <is>
-          <t>AD 11/25/2025 row 1639; 4_Item Detail rows 19, 57 (col V); 5_Exceptions row 8</t>
+          <t>E04 tabs 2_Cisco Network Administrators and 3_ISEAdmin, AD extract 11/25/2025, row 1639; 4_Item Detail rows 19, 57 (col V); 5_Exceptions row 8</t>
         </is>
       </c>
       <c r="E13" s="24" t="inlineStr">
@@ -1912,12 +1912,12 @@
       </c>
       <c r="C14" s="24" t="inlineStr">
         <is>
-          <t>E05 BSI.IT.27.C7.02 Q1 2026 Cert.xlsx; E06 walkthrough</t>
+          <t>E05 BSI.IT.27.C7_E05_Q1 2026 Cert.xlsx; E06 walkthrough</t>
         </is>
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>Rows 3260, 3265; 4_Item Detail rows 107, 130 (col U)</t>
+          <t>E05 tab 2.Cisco Network Administrators, rows 3260, 3265; 4_Item Detail rows 107, 130 (col U)</t>
         </is>
       </c>
       <c r="E14" s="24" t="inlineStr">
@@ -2212,7 +2212,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>SailPoint export, AD extract, Netwrix log</t>
+          <t>SailPoint export, AD extract, Netwrix log (tabs 1_Cisco ISE Administrators, 2_Cisco Network Administrators, 3_ISEAdmin, 4_F5FullAdmin; Netwrix in section REVOCATION EVIDENCE of tabs 2-3)</t>
         </is>
       </c>
       <c r="D8" s="24" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="C9" s="24" t="inlineStr">
         <is>
-          <t>SailPoint export, AD extract</t>
+          <t>SailPoint export, AD extract (tabs 1.Cisco ISE Administrators, 2.Cisco Network Administrators, 3.ISEAdmin, 4.F5FullAdmin)</t>
         </is>
       </c>
       <c r="D9" s="24" t="inlineStr">
